--- a/task157/golden/signature_projection_2028.xlsx
+++ b/task157/golden/signature_projection_2028.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
   <si>
     <t>Projection for initiative serial I-18-2028</t>
   </si>
@@ -97,10 +97,7 @@
     <t>County name</t>
   </si>
   <si>
-    <t>Signatures the recorder determined</t>
-  </si>
-  <si>
-    <t>Registered when signed, no longer valid</t>
+    <t>In force when signed, cancelled in the 10 July 2028 snapshot</t>
   </si>
   <si>
     <t>01</t>
@@ -251,9 +248,6 @@
   </si>
   <si>
     <t>Sampled signatures signed</t>
-  </si>
-  <si>
-    <t>Petition sheet serials</t>
   </si>
   <si>
     <t>Prepared by</t>
@@ -744,7 +738,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>20669</v>
+        <v>20662</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -752,7 +746,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>6270</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -769,7 +763,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>125400</v>
+        <v>125540</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -785,7 +779,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="4">
-        <v>390200</v>
+        <v>390060</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -801,7 +795,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="5">
-        <v>101.4</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -824,16 +818,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{911CDDDD-A3CD-5993-9463-986C7BABF69C}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
@@ -843,218 +836,170 @@
       <c r="C1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2">
-        <v>243</v>
-      </c>
-      <c r="D2" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="2">
-        <v>503</v>
-      </c>
-      <c r="D3" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2">
-        <v>544</v>
-      </c>
-      <c r="D4" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="2">
-        <v>223</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="2">
-        <v>124</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2">
-        <v>81</v>
-      </c>
-      <c r="D8" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="2">
-        <v>16714</v>
-      </c>
-      <c r="D9" s="2">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2">
-        <v>820</v>
-      </c>
-      <c r="D10" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="2">
-        <v>357</v>
-      </c>
-      <c r="D11" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="2">
-        <v>3966</v>
-      </c>
-      <c r="D12" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>48</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2">
-        <v>1441</v>
-      </c>
-      <c r="D13" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>50</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="2">
-        <v>162</v>
-      </c>
-      <c r="D14" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>52</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="2">
-        <v>1070</v>
-      </c>
-      <c r="D15" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
       <c r="C16" s="2">
-        <v>529</v>
-      </c>
-      <c r="D16" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1076,336 +1021,336 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>62</v>
       </c>
-      <c r="C2" t="s">
-        <v>63</v>
-      </c>
       <c r="D2" s="2">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="E2" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" t="s">
-        <v>62</v>
-      </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="E3" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2">
-        <v>2246</v>
+        <v>2180</v>
       </c>
       <c r="E4" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="E5" s="2">
-        <v>514</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2">
-        <v>2350</v>
+        <v>2332</v>
       </c>
       <c r="E6" s="2">
-        <v>561</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2">
-        <v>1042</v>
+        <v>971</v>
       </c>
       <c r="E7" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
         <v>69</v>
       </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
         <v>69</v>
       </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2">
-        <v>830</v>
+        <v>906</v>
       </c>
       <c r="E9" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
         <v>69</v>
       </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2">
-        <v>1544</v>
+        <v>1589</v>
       </c>
       <c r="E10" s="2">
-        <v>366</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11" s="2">
-        <v>1789</v>
+        <v>1882</v>
       </c>
       <c r="E11" s="2">
-        <v>392</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
         <v>69</v>
       </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2">
-        <v>1715</v>
+        <v>2033</v>
       </c>
       <c r="E12" s="2">
-        <v>424</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13" s="2">
-        <v>991</v>
+        <v>1251</v>
       </c>
       <c r="E13" s="2">
-        <v>225</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2">
         <v>45</v>
       </c>
       <c r="E14" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="E15" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
         <v>71</v>
       </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="2">
-        <v>938</v>
+        <v>839</v>
       </c>
       <c r="E16" s="2">
-        <v>219</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
         <v>71</v>
       </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="2">
-        <v>1281</v>
+        <v>1151</v>
       </c>
       <c r="E17" s="2">
-        <v>288</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
         <v>71</v>
       </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2">
-        <v>1555</v>
+        <v>1276</v>
       </c>
       <c r="E18" s="2">
-        <v>342</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
         <v>71</v>
       </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2">
-        <v>1504</v>
+        <v>1268</v>
       </c>
       <c r="E19" s="2">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
         <v>73</v>
       </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
@@ -1416,87 +1361,87 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E21" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="2">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="E22" s="2">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
         <v>73</v>
       </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="2">
-        <v>705</v>
+        <v>788</v>
       </c>
       <c r="E23" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="2">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="E24" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="2">
-        <v>1571</v>
+        <v>1547</v>
       </c>
       <c r="E25" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -1511,84 +1456,84 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="C2" s="2">
-        <v>776</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2">
-        <v>2902</v>
+        <v>2964</v>
       </c>
       <c r="C3" s="2">
-        <v>2125</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2">
-        <v>5151</v>
+        <v>5075</v>
       </c>
       <c r="C4" s="2">
-        <v>3841</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="2">
-        <v>6085</v>
+        <v>6141</v>
       </c>
       <c r="C5" s="2">
-        <v>4482</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2">
-        <v>6553</v>
+        <v>6567</v>
       </c>
       <c r="C6" s="2">
-        <v>4846</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2">
-        <v>5108</v>
+        <v>5037</v>
       </c>
       <c r="C7" s="2">
-        <v>3737</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1612,63 +1557,63 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/task157/golden/signature_projection_2028.xlsx
+++ b/task157/golden/signature_projection_2028.xlsx
@@ -277,7 +277,7 @@
     <t>A sheet is identified by the circulator's registration number with the sheet number, because each firm numbered its own sheets.</t>
   </si>
   <si>
-    <t>County figures are over the lines each recorder determined; the lines the division determined are left out of them.</t>
+    <t>County figures are over the lines each county's own recorder determined, whatever disposition code it gave; the lines the division determined are left out of them.</t>
   </si>
   <si>
     <t>A signature belongs to the firm that had its circulator registered on the day it was given; twenty-two circulators registered again under another firm inside the window.</t>
